--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96773</v>
+        <v>96776</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96557</v>
+        <v>96560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96776</v>
+        <v>96777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96560</v>
+        <v>96561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>120512487</v>
       </c>
       <c r="B3" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         <v>128354132</v>
       </c>
       <c r="B4" t="n">
-        <v>96777</v>
+        <v>96782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96561</v>
+        <v>96566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58019</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96566</v>
+        <v>96568</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96568</v>
+        <v>96574</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96574</v>
+        <v>96576</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96576</v>
+        <v>96577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96577</v>
+        <v>96583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96583</v>
+        <v>96587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1966,7 +1966,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96587</v>
+        <v>96589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96589</v>
+        <v>96591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1291,7 +1291,7 @@
         <v>136595636</v>
       </c>
       <c r="B7" t="n">
-        <v>96591</v>
+        <v>96604</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>136595638</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1880,11 +1880,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergebäcken, Mpd</t>
@@ -1992,16 +1988,8 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergebäcken, Bergebäcken, Mpd</t>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 46124-2024 artfynd.xlsx
+++ b/artfynd/A 46124-2024 artfynd.xlsx
@@ -1854,7 +1854,7 @@
         <v>136595639</v>
       </c>
       <c r="B12" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>120513158</v>
       </c>
       <c r="B13" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
